--- a/VerveStacks_IND_grids_kan10/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_IND_grids_kan10/ReportDefs_vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E6153CB-BC7F-4EE0-B672-E319780C4AFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A08EB83-CA55-4E81-ADD9-14BBE0FF8E1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="geolocation" sheetId="72" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7179" uniqueCount="997">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7203" uniqueCount="1005">
   <si>
     <t>Unit</t>
   </si>
@@ -3074,6 +3074,30 @@
   </si>
   <si>
     <t>grid,aggregators</t>
+  </si>
+  <si>
+    <t>base·$600·Y·100%</t>
+  </si>
+  <si>
+    <t>high·$600·Y·100%</t>
+  </si>
+  <si>
+    <t>base·$600·N·100%</t>
+  </si>
+  <si>
+    <t>high·$600·N·100%</t>
+  </si>
+  <si>
+    <t>base·$600·Y·001%</t>
+  </si>
+  <si>
+    <t>high·$600·Y·001%</t>
+  </si>
+  <si>
+    <t>base·$600·N·001%</t>
+  </si>
+  <si>
+    <t>high·$600·N·001%</t>
   </si>
 </sst>
 </file>
@@ -32965,7 +32989,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C50B696F-B355-4FC5-AD3E-AFDC509F717D}">
-  <dimension ref="B2:T37"/>
+  <dimension ref="B2:T45"/>
   <sheetFormatPr defaultColWidth="14.73046875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="2.73046875" bestFit="1" customWidth="1"/>
@@ -34698,6 +34722,414 @@
         <v>960</v>
       </c>
       <c r="T37">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="38" spans="2:20">
+      <c r="B38" t="str">
+        <f t="shared" ref="B38:B45" si="7">"vs~"&amp;TEXT(P38,"0000")</f>
+        <v>vs~0033</v>
+      </c>
+      <c r="C38" t="str">
+        <f t="shared" ref="C38:C45" si="8">H38</f>
+        <v>base·$600·Y·100%</v>
+      </c>
+      <c r="H38" t="str">
+        <f t="shared" ref="H38:H45" si="9">O38</f>
+        <v>base·$600·Y·100%</v>
+      </c>
+      <c r="I38" t="str">
+        <f t="shared" ref="I38:I45" si="10">Q38</f>
+        <v>base</v>
+      </c>
+      <c r="J38" t="str">
+        <f t="shared" ref="J38:J45" si="11">TEXT(R38,"$000")</f>
+        <v>$600</v>
+      </c>
+      <c r="K38" t="str">
+        <f t="shared" ref="K38:K45" si="12">S38</f>
+        <v>Y</v>
+      </c>
+      <c r="L38" t="str">
+        <f t="shared" ref="L38:L45" si="13">TEXT(T38,"000%")</f>
+        <v>100%</v>
+      </c>
+      <c r="N38">
+        <v>5</v>
+      </c>
+      <c r="O38" t="s">
+        <v>997</v>
+      </c>
+      <c r="P38">
+        <v>33</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>347</v>
+      </c>
+      <c r="R38">
+        <v>600</v>
+      </c>
+      <c r="S38" t="s">
+        <v>951</v>
+      </c>
+      <c r="T38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20">
+      <c r="B39" t="str">
+        <f t="shared" si="7"/>
+        <v>vs~0034</v>
+      </c>
+      <c r="C39" t="str">
+        <f t="shared" si="8"/>
+        <v>high·$600·Y·100%</v>
+      </c>
+      <c r="H39" t="str">
+        <f t="shared" si="9"/>
+        <v>high·$600·Y·100%</v>
+      </c>
+      <c r="I39" t="str">
+        <f t="shared" si="10"/>
+        <v>high</v>
+      </c>
+      <c r="J39" t="str">
+        <f t="shared" si="11"/>
+        <v>$600</v>
+      </c>
+      <c r="K39" t="str">
+        <f t="shared" si="12"/>
+        <v>Y</v>
+      </c>
+      <c r="L39" t="str">
+        <f t="shared" si="13"/>
+        <v>100%</v>
+      </c>
+      <c r="N39">
+        <v>5</v>
+      </c>
+      <c r="O39" t="s">
+        <v>998</v>
+      </c>
+      <c r="P39">
+        <v>34</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>348</v>
+      </c>
+      <c r="R39">
+        <v>600</v>
+      </c>
+      <c r="S39" t="s">
+        <v>951</v>
+      </c>
+      <c r="T39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="2:20">
+      <c r="B40" t="str">
+        <f t="shared" si="7"/>
+        <v>vs~0035</v>
+      </c>
+      <c r="C40" t="str">
+        <f t="shared" si="8"/>
+        <v>base·$600·N·100%</v>
+      </c>
+      <c r="H40" t="str">
+        <f t="shared" si="9"/>
+        <v>base·$600·N·100%</v>
+      </c>
+      <c r="I40" t="str">
+        <f t="shared" si="10"/>
+        <v>base</v>
+      </c>
+      <c r="J40" t="str">
+        <f t="shared" si="11"/>
+        <v>$600</v>
+      </c>
+      <c r="K40" t="str">
+        <f t="shared" si="12"/>
+        <v>N</v>
+      </c>
+      <c r="L40" t="str">
+        <f t="shared" si="13"/>
+        <v>100%</v>
+      </c>
+      <c r="N40">
+        <v>5</v>
+      </c>
+      <c r="O40" t="s">
+        <v>999</v>
+      </c>
+      <c r="P40">
+        <v>35</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>347</v>
+      </c>
+      <c r="R40">
+        <v>600</v>
+      </c>
+      <c r="S40" t="s">
+        <v>960</v>
+      </c>
+      <c r="T40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="2:20">
+      <c r="B41" t="str">
+        <f t="shared" si="7"/>
+        <v>vs~0036</v>
+      </c>
+      <c r="C41" t="str">
+        <f t="shared" si="8"/>
+        <v>high·$600·N·100%</v>
+      </c>
+      <c r="H41" t="str">
+        <f t="shared" si="9"/>
+        <v>high·$600·N·100%</v>
+      </c>
+      <c r="I41" t="str">
+        <f t="shared" si="10"/>
+        <v>high</v>
+      </c>
+      <c r="J41" t="str">
+        <f t="shared" si="11"/>
+        <v>$600</v>
+      </c>
+      <c r="K41" t="str">
+        <f t="shared" si="12"/>
+        <v>N</v>
+      </c>
+      <c r="L41" t="str">
+        <f t="shared" si="13"/>
+        <v>100%</v>
+      </c>
+      <c r="N41">
+        <v>5</v>
+      </c>
+      <c r="O41" t="s">
+        <v>1000</v>
+      </c>
+      <c r="P41">
+        <v>36</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>348</v>
+      </c>
+      <c r="R41">
+        <v>600</v>
+      </c>
+      <c r="S41" t="s">
+        <v>960</v>
+      </c>
+      <c r="T41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20">
+      <c r="B42" t="str">
+        <f t="shared" si="7"/>
+        <v>vs~0037</v>
+      </c>
+      <c r="C42" t="str">
+        <f t="shared" si="8"/>
+        <v>base·$600·Y·001%</v>
+      </c>
+      <c r="H42" t="str">
+        <f t="shared" si="9"/>
+        <v>base·$600·Y·001%</v>
+      </c>
+      <c r="I42" t="str">
+        <f t="shared" si="10"/>
+        <v>base</v>
+      </c>
+      <c r="J42" t="str">
+        <f t="shared" si="11"/>
+        <v>$600</v>
+      </c>
+      <c r="K42" t="str">
+        <f t="shared" si="12"/>
+        <v>Y</v>
+      </c>
+      <c r="L42" t="str">
+        <f t="shared" si="13"/>
+        <v>001%</v>
+      </c>
+      <c r="N42">
+        <v>5</v>
+      </c>
+      <c r="O42" t="s">
+        <v>1001</v>
+      </c>
+      <c r="P42">
+        <v>37</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>347</v>
+      </c>
+      <c r="R42">
+        <v>600</v>
+      </c>
+      <c r="S42" t="s">
+        <v>951</v>
+      </c>
+      <c r="T42">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20">
+      <c r="B43" t="str">
+        <f t="shared" si="7"/>
+        <v>vs~0038</v>
+      </c>
+      <c r="C43" t="str">
+        <f t="shared" si="8"/>
+        <v>high·$600·Y·001%</v>
+      </c>
+      <c r="H43" t="str">
+        <f t="shared" si="9"/>
+        <v>high·$600·Y·001%</v>
+      </c>
+      <c r="I43" t="str">
+        <f t="shared" si="10"/>
+        <v>high</v>
+      </c>
+      <c r="J43" t="str">
+        <f t="shared" si="11"/>
+        <v>$600</v>
+      </c>
+      <c r="K43" t="str">
+        <f t="shared" si="12"/>
+        <v>Y</v>
+      </c>
+      <c r="L43" t="str">
+        <f t="shared" si="13"/>
+        <v>001%</v>
+      </c>
+      <c r="N43">
+        <v>5</v>
+      </c>
+      <c r="O43" t="s">
+        <v>1002</v>
+      </c>
+      <c r="P43">
+        <v>38</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>348</v>
+      </c>
+      <c r="R43">
+        <v>600</v>
+      </c>
+      <c r="S43" t="s">
+        <v>951</v>
+      </c>
+      <c r="T43">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20">
+      <c r="B44" t="str">
+        <f t="shared" si="7"/>
+        <v>vs~0039</v>
+      </c>
+      <c r="C44" t="str">
+        <f t="shared" si="8"/>
+        <v>base·$600·N·001%</v>
+      </c>
+      <c r="H44" t="str">
+        <f t="shared" si="9"/>
+        <v>base·$600·N·001%</v>
+      </c>
+      <c r="I44" t="str">
+        <f t="shared" si="10"/>
+        <v>base</v>
+      </c>
+      <c r="J44" t="str">
+        <f t="shared" si="11"/>
+        <v>$600</v>
+      </c>
+      <c r="K44" t="str">
+        <f t="shared" si="12"/>
+        <v>N</v>
+      </c>
+      <c r="L44" t="str">
+        <f t="shared" si="13"/>
+        <v>001%</v>
+      </c>
+      <c r="N44">
+        <v>5</v>
+      </c>
+      <c r="O44" t="s">
+        <v>1003</v>
+      </c>
+      <c r="P44">
+        <v>39</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>347</v>
+      </c>
+      <c r="R44">
+        <v>600</v>
+      </c>
+      <c r="S44" t="s">
+        <v>960</v>
+      </c>
+      <c r="T44">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20">
+      <c r="B45" t="str">
+        <f t="shared" si="7"/>
+        <v>vs~0040</v>
+      </c>
+      <c r="C45" t="str">
+        <f t="shared" si="8"/>
+        <v>high·$600·N·001%</v>
+      </c>
+      <c r="H45" t="str">
+        <f t="shared" si="9"/>
+        <v>high·$600·N·001%</v>
+      </c>
+      <c r="I45" t="str">
+        <f t="shared" si="10"/>
+        <v>high</v>
+      </c>
+      <c r="J45" t="str">
+        <f t="shared" si="11"/>
+        <v>$600</v>
+      </c>
+      <c r="K45" t="str">
+        <f t="shared" si="12"/>
+        <v>N</v>
+      </c>
+      <c r="L45" t="str">
+        <f t="shared" si="13"/>
+        <v>001%</v>
+      </c>
+      <c r="N45">
+        <v>5</v>
+      </c>
+      <c r="O45" t="s">
+        <v>1004</v>
+      </c>
+      <c r="P45">
+        <v>40</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>348</v>
+      </c>
+      <c r="R45">
+        <v>600</v>
+      </c>
+      <c r="S45" t="s">
+        <v>960</v>
+      </c>
+      <c r="T45">
         <v>0.01</v>
       </c>
     </row>

--- a/VerveStacks_IND_grids_kan10/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_IND_grids_kan10/ReportDefs_vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A08EB83-CA55-4E81-ADD9-14BBE0FF8E1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7734A0A3-1296-4EE1-A532-0803EA158071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="geolocation" sheetId="72" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7203" uniqueCount="1005">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7204" uniqueCount="1005">
   <si>
     <t>Unit</t>
   </si>
@@ -3064,12 +3064,6 @@
     <t>Price_Fuel</t>
   </si>
   <si>
-    <t>DEM</t>
-  </si>
-  <si>
-    <t>elc_*</t>
-  </si>
-  <si>
     <t>Price_Electricity</t>
   </si>
   <si>
@@ -3098,6 +3092,12 @@
   </si>
   <si>
     <t>high·$600·N·001%</t>
+  </si>
+  <si>
+    <t>e[_]*,ELC</t>
+  </si>
+  <si>
+    <t>Marginal value of produced electricity</t>
   </si>
 </sst>
 </file>
@@ -34758,7 +34758,7 @@
         <v>5</v>
       </c>
       <c r="O38" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="P38">
         <v>33</v>
@@ -34809,7 +34809,7 @@
         <v>5</v>
       </c>
       <c r="O39" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="P39">
         <v>34</v>
@@ -34860,7 +34860,7 @@
         <v>5</v>
       </c>
       <c r="O40" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="P40">
         <v>35</v>
@@ -34911,7 +34911,7 @@
         <v>5</v>
       </c>
       <c r="O41" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="P41">
         <v>36</v>
@@ -34962,7 +34962,7 @@
         <v>5</v>
       </c>
       <c r="O42" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="P42">
         <v>37</v>
@@ -35013,7 +35013,7 @@
         <v>5</v>
       </c>
       <c r="O43" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="P43">
         <v>38</v>
@@ -35064,7 +35064,7 @@
         <v>5</v>
       </c>
       <c r="O44" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="P44">
         <v>39</v>
@@ -35115,7 +35115,7 @@
         <v>5</v>
       </c>
       <c r="O45" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="P45">
         <v>40</v>
@@ -35576,16 +35576,19 @@
         <v>49</v>
       </c>
       <c r="H20" t="s">
-        <v>993</v>
+        <v>25</v>
       </c>
       <c r="I20" t="s">
-        <v>994</v>
+        <v>1003</v>
       </c>
       <c r="K20" t="s">
         <v>287</v>
       </c>
       <c r="N20" t="s">
-        <v>995</v>
+        <v>993</v>
+      </c>
+      <c r="P20" t="s">
+        <v>1004</v>
       </c>
       <c r="Q20" t="s">
         <v>109</v>
@@ -35658,7 +35661,7 @@
         <v>6</v>
       </c>
       <c r="C25" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="K25" t="s">
         <v>7</v>
@@ -35672,7 +35675,7 @@
         <v>34</v>
       </c>
       <c r="C26" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="K26" t="s">
         <v>7</v>

--- a/VerveStacks_IND_grids_kan10/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_IND_grids_kan10/ReportDefs_vervestacks.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_IND_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7734A0A3-1296-4EE1-A532-0803EA158071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B274EDFE-8ADA-4080-8920-0498F45317C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="geolocation" sheetId="72" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7204" uniqueCount="1005">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7232" uniqueCount="1014">
   <si>
     <t>Unit</t>
   </si>
@@ -3098,6 +3098,33 @@
   </si>
   <si>
     <t>Marginal value of produced electricity</t>
+  </si>
+  <si>
+    <t>m$</t>
+  </si>
+  <si>
+    <t>z_Elecprodcost</t>
+  </si>
+  <si>
+    <t>Cost_Flox</t>
+  </si>
+  <si>
+    <t>ELE,CHP</t>
+  </si>
+  <si>
+    <t>NRG,ENV</t>
+  </si>
+  <si>
+    <t>-ELC,-e{_]*</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>Avg_cost_elec</t>
+  </si>
+  <si>
+    <t>scalar</t>
   </si>
 </sst>
 </file>
@@ -35142,7 +35169,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet19"/>
-  <dimension ref="A1:U31"/>
+  <dimension ref="A1:U36"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.86328125" bestFit="1" customWidth="1"/>
@@ -35787,6 +35814,85 @@
         <v>38</v>
       </c>
     </row>
+    <row r="32" spans="1:17">
+      <c r="A32" t="s">
+        <v>280</v>
+      </c>
+      <c r="C32" t="s">
+        <v>1008</v>
+      </c>
+      <c r="K32" t="s">
+        <v>1005</v>
+      </c>
+      <c r="N32" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17">
+      <c r="A33" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C33" t="s">
+        <v>1008</v>
+      </c>
+      <c r="K33" t="s">
+        <v>1005</v>
+      </c>
+      <c r="N33" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17">
+      <c r="A34" t="s">
+        <v>281</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1008</v>
+      </c>
+      <c r="K34" t="s">
+        <v>1005</v>
+      </c>
+      <c r="N34" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17">
+      <c r="A35" t="s">
+        <v>279</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1008</v>
+      </c>
+      <c r="K35" t="s">
+        <v>1005</v>
+      </c>
+      <c r="N35" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17">
+      <c r="A36" t="s">
+        <v>278</v>
+      </c>
+      <c r="C36" t="s">
+        <v>1008</v>
+      </c>
+      <c r="H36" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>1010</v>
+      </c>
+      <c r="K36" t="s">
+        <v>1005</v>
+      </c>
+      <c r="N36" t="s">
+        <v>1006</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>1011</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="T4:U4"/>
@@ -35799,7 +35905,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68A8EC7F-95E3-4526-8B78-C58A96098159}">
-  <dimension ref="C1:K3"/>
+  <dimension ref="C1:L6"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="3" max="3" width="17.53125" bestFit="1" customWidth="1"/>
@@ -35813,12 +35919,12 @@
     <col min="11" max="11" width="12.46484375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:11">
+    <row r="1" spans="3:12">
       <c r="C1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="3:11">
+    <row r="2" spans="3:12">
       <c r="C2" t="s">
         <v>95</v>
       </c>
@@ -35844,10 +35950,13 @@
         <v>99</v>
       </c>
       <c r="K2" t="s">
+        <v>1013</v>
+      </c>
+      <c r="L2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="3:11">
+    <row r="3" spans="3:12">
       <c r="C3" t="s">
         <v>73</v>
       </c>
@@ -35868,6 +35977,30 @@
       </c>
       <c r="J3" t="s">
         <v>38</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="3:12">
+      <c r="C6" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D6" t="str">
+        <f>C3</f>
+        <v>Elec Production</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F6" t="s">
+        <v>287</v>
+      </c>
+      <c r="J6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_IND_grids_kan10/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_IND_grids_kan10/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_IND_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B274EDFE-8ADA-4080-8920-0498F45317C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AE7DD0E-79A0-4E5B-9424-C599D03B6F19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35905,7 +35905,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68A8EC7F-95E3-4526-8B78-C58A96098159}">
-  <dimension ref="C1:L6"/>
+  <dimension ref="C1:L4"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="3" max="3" width="17.53125" bestFit="1" customWidth="1"/>
@@ -35982,24 +35982,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="3:12">
-      <c r="C6" t="s">
+    <row r="4" spans="3:12">
+      <c r="C4" t="s">
         <v>1006</v>
       </c>
-      <c r="D6" t="str">
+      <c r="D4" t="str">
         <f>C3</f>
         <v>Elec Production</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E4" t="s">
         <v>1012</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F4" t="s">
         <v>287</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J4" t="s">
         <v>38</v>
       </c>
-      <c r="K6">
+      <c r="K4">
         <v>0</v>
       </c>
     </row>

--- a/VerveStacks_IND_grids_kan10/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_IND_grids_kan10/ReportDefs_vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_IND_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AE7DD0E-79A0-4E5B-9424-C599D03B6F19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EADE0D30-35CE-45A0-9A25-611AD2129EB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="geolocation" sheetId="72" r:id="rId1"/>
@@ -3115,9 +3115,6 @@
     <t>NRG,ENV</t>
   </si>
   <si>
-    <t>-ELC,-e{_]*</t>
-  </si>
-  <si>
     <t>c</t>
   </si>
   <si>
@@ -3125,6 +3122,9 @@
   </si>
   <si>
     <t>scalar</t>
+  </si>
+  <si>
+    <t>-ELC*,-e[_]*</t>
   </si>
 </sst>
 </file>
@@ -35881,7 +35881,7 @@
         <v>1009</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="K36" t="s">
         <v>1005</v>
@@ -35890,7 +35890,7 @@
         <v>1006</v>
       </c>
       <c r="Q36" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
   </sheetData>
@@ -35950,7 +35950,7 @@
         <v>99</v>
       </c>
       <c r="K2" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="L2" t="s">
         <v>9</v>
@@ -35991,7 +35991,7 @@
         <v>Elec Production</v>
       </c>
       <c r="E4" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="F4" t="s">
         <v>287</v>
